--- a/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,26; 41,43</t>
+          <t>25,1; 42,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,27; 42,0</t>
+          <t>25,2; 40,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,69; 38,58</t>
+          <t>27,29; 38,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,54; 43,52</t>
+          <t>26,51; 43,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,3; 43,85</t>
+          <t>27,02; 44,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,64; 40,79</t>
+          <t>29,1; 41,34</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 53,46</t>
+          <t>30,8; 54,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 52,53</t>
+          <t>29,29; 51,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,42; 49,07</t>
+          <t>32,73; 49,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 63,68</t>
+          <t>34,1; 64,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,01; 40,31</t>
+          <t>27,54; 39,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,0; 51,05</t>
+          <t>33,31; 52,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,65; 58,39</t>
+          <t>42,11; 58,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 51,39</t>
+          <t>34,15; 51,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,1; 51,75</t>
+          <t>38,9; 51,46</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,9; 65,54</t>
+          <t>44,51; 65,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,56; 60,9</t>
+          <t>40,3; 61,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,35; 61,16</t>
+          <t>45,68; 60,35</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,97; 51,49</t>
+          <t>38,93; 50,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,28; 41,47</t>
+          <t>34,45; 41,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,69; 44,71</t>
+          <t>37,61; 44,69</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34369</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>44554</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>78923</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26215; 43954</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>34268; 55468</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>65620; 93556</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33206</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>33929</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>67135</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25099; 40960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25822; 42081</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>55368; 78644</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>25321</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>47105</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15971; 28307</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18705; 32795</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>37869; 57519</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>73001</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>169457</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74283; 141274</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>60107; 86044</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>145247; 230353</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59265</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>70884</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>130149</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>50291; 69380</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>55540; 83437</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>109724; 145137</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37932</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>36810</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>74742</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>30667; 45080</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>29020; 44580</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>64366; 85032</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>283012</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>284499</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>567510</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>255805; 333111</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>257752; 308203</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>528514; 628142</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,1; 42,08</t>
+          <t>25,26; 42,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,2; 40,8</t>
+          <t>24,92; 41,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,29; 38,91</t>
+          <t>27,54; 39,34</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,51; 43,26</t>
+          <t>26,98; 43,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,02; 44,03</t>
+          <t>26,18; 43,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 41,34</t>
+          <t>29,48; 41,26</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 54,58</t>
+          <t>30,68; 53,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,29; 51,36</t>
+          <t>29,4; 52,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,73; 49,71</t>
+          <t>32,63; 49,9</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,1; 64,86</t>
+          <t>34,01; 64,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 39,42</t>
+          <t>28,07; 40,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,31; 52,82</t>
+          <t>32,93; 51,5</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,11; 58,09</t>
+          <t>42,22; 57,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 51,31</t>
+          <t>33,55; 52,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,9; 51,46</t>
+          <t>38,33; 51,6</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,51; 65,43</t>
+          <t>44,69; 66,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,3; 61,91</t>
+          <t>40,93; 62,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,68; 60,35</t>
+          <t>45,6; 60,24</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,93; 50,69</t>
+          <t>38,96; 50,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,45; 41,19</t>
+          <t>34,66; 41,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,61; 44,69</t>
+          <t>37,93; 44,68</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26215; 43954</t>
+          <t>26388; 43942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34268; 55468</t>
+          <t>33877; 55754</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65620; 93556</t>
+          <t>66217; 94595</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25099; 40960</t>
+          <t>25548; 41073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25822; 42081</t>
+          <t>25021; 41680</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55368; 78644</t>
+          <t>56086; 78496</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15971; 28307</t>
+          <t>15910; 27922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18705; 32795</t>
+          <t>18772; 33771</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37869; 57519</t>
+          <t>37761; 57746</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74283; 141274</t>
+          <t>74080; 140054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60107; 86044</t>
+          <t>61264; 87818</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>145247; 230353</t>
+          <t>143619; 224587</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50291; 69380</t>
+          <t>50428; 68646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55540; 83437</t>
+          <t>54564; 84862</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>109724; 145137</t>
+          <t>108098; 145538</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30667; 45080</t>
+          <t>30790; 45557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29020; 44580</t>
+          <t>29473; 45105</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64366; 85032</t>
+          <t>64256; 84873</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255805; 333111</t>
+          <t>256028; 332084</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>257752; 308203</t>
+          <t>259377; 309683</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>528514; 628142</t>
+          <t>533047; 627976</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,26; 42,07</t>
+          <t>26,49; 41,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 41,01</t>
+          <t>23,83; 39,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,54; 39,34</t>
+          <t>27,04; 37,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,98; 43,38</t>
+          <t>26,89; 45,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 43,61</t>
+          <t>27,46; 44,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,48; 41,26</t>
+          <t>30,7; 42,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,68; 53,84</t>
+          <t>27,83; 51,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,4; 52,89</t>
+          <t>31,36; 54,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,63; 49,9</t>
+          <t>32,87; 49,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 64,3</t>
+          <t>28,26; 40,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,07; 40,23</t>
+          <t>29,86; 41,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,93; 51,5</t>
+          <t>30,85; 39,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,22; 57,48</t>
+          <t>34,66; 52,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,55; 52,19</t>
+          <t>42,38; 57,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,33; 51,6</t>
+          <t>40,6; 52,35</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,69; 66,12</t>
+          <t>41,2; 62,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,93; 62,64</t>
+          <t>43,01; 65,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,6; 60,24</t>
+          <t>45,92; 61,83</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,96; 50,53</t>
+          <t>35,39; 42,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,66; 41,39</t>
+          <t>37,32; 44,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,93; 44,68</t>
+          <t>37,21; 42,26</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1806,27 +1806,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34369</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78923</t>
+          <t>73766</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26388; 43942</t>
+          <t>32218; 51059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33877; 55754</t>
+          <t>24532; 40500</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66217; 94595</t>
+          <t>60722; 85270</t>
         </is>
       </c>
     </row>
@@ -2014,27 +2014,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67135</t>
+          <t>68690</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25548; 41073</t>
+          <t>24575; 41553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25021; 41680</t>
+          <t>26510; 43143</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56086; 78496</t>
+          <t>57690; 79145</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>45133</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15910; 27922</t>
+          <t>15845; 29575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18772; 33771</t>
+          <t>16774; 29102</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37761; 57746</t>
+          <t>36293; 55174</t>
         </is>
       </c>
     </row>
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96456</t>
+          <t>68525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>169457</t>
+          <t>132369</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74080; 140054</t>
+          <t>57068; 82381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61264; 87818</t>
+          <t>53330; 74318</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>143619; 224587</t>
+          <t>117409; 149330</t>
         </is>
       </c>
     </row>
@@ -2638,27 +2638,27 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59265</t>
+          <t>66360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>130149</t>
+          <t>125168</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50428; 68646</t>
+          <t>51379; 78028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54564; 84862</t>
+          <t>50320; 68010</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>108098; 145538</t>
+          <t>108402; 139774</t>
         </is>
       </c>
     </row>
@@ -2846,27 +2846,27 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74742</t>
+          <t>74390</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30790; 45557</t>
+          <t>28136; 42590</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29473; 45105</t>
+          <t>30257; 46079</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64256; 84873</t>
+          <t>63670; 85724</t>
         </is>
       </c>
     </row>
@@ -3054,27 +3054,27 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>363</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>283012</t>
+          <t>267990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>284499</t>
+          <t>251525</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>567510</t>
+          <t>519515</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>256028; 332084</t>
+          <t>243646; 290736</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>259377; 309683</t>
+          <t>231628; 274007</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>533047; 627976</t>
+          <t>487057; 553181</t>
         </is>
       </c>
     </row>
